--- a/TT_Nat_Gas_Prod_Util_2026.xlsx
+++ b/TT_Nat_Gas_Prod_Util_2026.xlsx
@@ -1,58 +1,142 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python-Projects\TT-Economic-Markers\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DA206C-25A3-44D3-B697-20D8D82B1028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="TT_Nat_Gas_Prod" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TT_Nat_Gas_Prod" sheetId="1" r:id="rId1"/>
+    <sheet name="TT_Nat_Gas_Prod Copy" sheetId="2" r:id="rId2"/>
+    <sheet name="Downstream Gas Util" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="21">
+  <si>
+    <t>Oct '20/ 
+Sep '21</t>
+  </si>
+  <si>
+    <t>Oct '21/ 
+Sep '22</t>
+  </si>
+  <si>
+    <t>Oct '22/ 
+Sep '23</t>
+  </si>
+  <si>
+    <t>Oct '23/ 
+Sep '24</t>
+  </si>
+  <si>
+    <t>Oct '24/ 
+Sep '25</t>
+  </si>
+  <si>
+    <t>Oct '24/ 
+May '25</t>
+  </si>
+  <si>
+    <t>Oct '25/ 
+May '26p</t>
+  </si>
+  <si>
+    <t>Natural Gas Production (MMSCF/D)</t>
+  </si>
+  <si>
+    <t>Natural Gas Utilisation (MMSCF/D)</t>
+  </si>
+  <si>
+    <t>Power Generation</t>
+  </si>
+  <si>
+    <t>Ammonia Manufacture</t>
+  </si>
+  <si>
+    <t>Methanol Manufacture</t>
+  </si>
+  <si>
+    <t>Refinery</t>
+  </si>
+  <si>
+    <t>Iron &amp; Steel Manufacture</t>
+  </si>
+  <si>
+    <t>Cement Manufacture</t>
+  </si>
+  <si>
+    <t>Ammonia Derivatives</t>
+  </si>
+  <si>
+    <t>Gas Processing</t>
+  </si>
+  <si>
+    <t>Gas to Liquids</t>
+  </si>
+  <si>
+    <t>NGC 4" Sales to bpTT</t>
+  </si>
+  <si>
+    <t>Small Consumers</t>
+  </si>
+  <si>
+    <t>Liquefied Natural Gas (LNG)</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,###.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F497D"/>
-        <bgColor rgb="001F497D"/>
+        <fgColor rgb="FF1F497D"/>
+        <bgColor rgb="FF1F497D"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,85 +153,1427 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="13"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-TT"/>
+              <a:t>T&amp;T Gas Utilisation per sector</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.31813128562392967"/>
+          <c:y val="4.8592592403645017E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.7740139037354041E-2"/>
+          <c:y val="2.2479175571190141E-2"/>
+          <c:w val="0.59969325507935745"/>
+          <c:h val="0.87981591570014239"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ammonia Manufacture</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F77B4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="1F77B4"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Oct '21/ 
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '22/ 
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '23/ 
+Sep '24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '24/ 
+Sep '25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '25/ 
+May '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$5:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>483.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>443.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>422.9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>462.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>345.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="1F77B4"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Methanol Manufacture</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="FF7F0E"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF7F0E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Oct '21/ 
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '22/ 
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '23/ 
+Sep '24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '24/ 
+Sep '25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '25/ 
+May '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$6:$F$6</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>516.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>534.4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>538.79999999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>452.2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>429.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="FF7F0E"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Refinery</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="2CA02C"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2CA02C"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Oct '21/ 
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '22/ 
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '23/ 
+Sep '24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '24/ 
+Sep '25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '25/ 
+May '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$7:$F$7</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="2CA02C"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Iron &amp; Steel Manufacture</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="D62728"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="D62728"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Oct '21/ 
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '22/ 
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '23/ 
+Sep '24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '24/ 
+Sep '25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '25/ 
+May '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$8:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>42.7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>39.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>46.3</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="D62728"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$9</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cement Manufacture</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="9467BD"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="9467BD"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Oct '21/ 
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '22/ 
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '23/ 
+Sep '24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '24/ 
+Sep '25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '25/ 
+May '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$9:$F$9</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>12.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>10.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="9467BD"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Ammonia Derivatives</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="8C564B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="8C564B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Oct '21/ 
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '22/ 
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '23/ 
+Sep '24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '24/ 
+Sep '25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '25/ 
+May '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$10:$F$10</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>19.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16.2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>19.7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="8C564B"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="6"/>
+          <c:order val="6"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$11</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Gas Processing</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="E377C2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="E377C2"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Oct '21/ 
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '22/ 
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '23/ 
+Sep '24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '24/ 
+Sep '25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '25/ 
+May '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$11:$F$11</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>18.899999999999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16.3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>18.3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>16.8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16.7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="E377C2"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="7"/>
+          <c:order val="7"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$12</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Gas to Liquids</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="7F7F7F"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="7F7F7F"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Oct '21/ 
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '22/ 
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '23/ 
+Sep '24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '24/ 
+Sep '25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '25/ 
+May '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$12:$F$12</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3.3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="7F7F7F"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="8"/>
+          <c:order val="8"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$13</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>NGC 4" Sales to bpTT</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="BCBD22"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="BCBD22"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Oct '21/ 
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '22/ 
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '23/ 
+Sep '24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '24/ 
+Sep '25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '25/ 
+May '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$13:$F$13</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="3">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="BCBD22"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="9"/>
+          <c:order val="9"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Small Consumers</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="17BECF"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="17BECF"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Oct '21/ 
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '22/ 
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '23/ 
+Sep '24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '24/ 
+Sep '25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '25/ 
+May '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$14:$F$14</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>9.3000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="17BECF"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="10"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Liquefied Natural Gas (LNG)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="34495E"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="34495E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$1:$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Oct '21/ 
+Sep '22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Oct '22/ 
+Sep '23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Oct '23/ 
+Sep '24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Oct '24/ 
+Sep '25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Oct '25/ 
+May '26p</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$15:$F$15</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1203.2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1171.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1071.5999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1137.0999999999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1157.5999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{6F2FDCE9-48DA-4B69-8628-5D25D57E5C99}">
+              <c14:invertSolidFillFmt>
+                <c14:spPr xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:solidFill>
+                      <a:srgbClr val="34495E"/>
+                    </a:solidFill>
+                    <a:prstDash val="solid"/>
+                  </a:ln>
+                </c14:spPr>
+              </c14:invertSolidFillFmt>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000A-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:overlap val="100"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$A$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Natural Gas Production (MMSCF/D)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="35000">
+              <a:solidFill>
+                <a:srgbClr val="2980B9"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'TT_Nat_Gas_Prod Copy'!$B$2:$F$2</c:f>
+              <c:numCache>
+                <c:formatCode>#,###.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2677.6</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2598.6999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2511.4</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2592.1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2442.1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-FC4B-40A7-9DBB-CD4DADB47851}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="10"/>
+        <c:axId val="300"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-TT"/>
+                  <a:t>Financial Year Period</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-TT"/>
+                  <a:t>Gas Volume Allocation (MMSCF/D)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="7.3397778509315392E-2"/>
+              <c:y val="0.3121549555277342"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="#,###.0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="300"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-TT"/>
+                  <a:t>Gas Production (MMSCF/D)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.73106314197049116"/>
+              <c:y val="0.51952384361028925"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="1"/>
+        </c:title>
+        <c:numFmt formatCode="#,###" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="10"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.72587316771403954"/>
+          <c:y val="2.5214900261631572E-2"/>
+          <c:w val="0.26531909886484267"/>
+          <c:h val="0.45149596791485958"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+</c:chartSpace>
+</file>
+
+<file path=xl/chartsheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartsheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</chartsheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:absoluteAnchor>
+    <xdr:pos x="0" y="0"/>
+    <xdr:ext cx="8651488" cy="6272561"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:absoluteAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -434,447 +1860,694 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '20/ 
-Sep '21</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '21/ 
-Sep '22</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '22/ 
-Sep '23</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '23/ 
-Sep '24</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '24/ 
-Sep '25</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '24/ 
-May '25</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Oct '25/ 
-May '26p</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Natural Gas Production (MMSCF/D)</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n">
+    <row r="1" spans="1:8" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3">
         <v>2574</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="C2" s="3">
         <v>2677.6</v>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>2598.7</v>
-      </c>
-      <c r="E2" s="3" t="n">
+      <c r="D2" s="3">
+        <v>2598.6999999999998</v>
+      </c>
+      <c r="E2" s="3">
         <v>2511.4</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="3">
         <v>2592.1</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="3">
         <v>2574.5</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="H2" s="3">
         <v>2442.1</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Natural Gas Utilisation (MMSCF/D)</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3">
         <v>2450</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="3">
         <v>2576.1</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="3">
         <v>2506.9</v>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>2394.7</v>
-      </c>
-      <c r="F3" s="3" t="n">
+      <c r="E3" s="3">
+        <v>2394.6999999999998</v>
+      </c>
+      <c r="F3" s="3">
         <v>2424</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="3">
         <v>2420.1</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="H3" s="3">
         <v>2273.4</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Power Generation</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="4">
         <v>245.2</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="4">
         <v>266.8</v>
       </c>
-      <c r="D4" s="4" t="n">
-        <v>258.1</v>
-      </c>
-      <c r="E4" s="4" t="n">
+      <c r="D4" s="4">
+        <v>258.10000000000002</v>
+      </c>
+      <c r="E4" s="4">
         <v>266.5</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="4">
         <v>268</v>
       </c>
-      <c r="G4" s="4" t="n">
-        <v>258.9</v>
-      </c>
-      <c r="H4" s="4" t="n">
+      <c r="G4" s="4">
+        <v>258.89999999999998</v>
+      </c>
+      <c r="H4" s="4">
         <v>250.9</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Ammonia Manufacture</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4">
         <v>503.1</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="4">
         <v>483.5</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="4">
         <v>443.7</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="4">
         <v>422.9</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="4">
         <v>462.3</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="4">
         <v>457.6</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="4">
         <v>345.1</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Methanol Manufacture</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="n">
-        <v>524.8</v>
-      </c>
-      <c r="C6" s="4" t="n">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4">
+        <v>524.79999999999995</v>
+      </c>
+      <c r="C6" s="4">
         <v>516.6</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="4">
         <v>534.4</v>
       </c>
-      <c r="E6" s="4" t="n">
-        <v>538.8</v>
-      </c>
-      <c r="F6" s="4" t="n">
+      <c r="E6" s="4">
+        <v>538.79999999999995</v>
+      </c>
+      <c r="F6" s="4">
         <v>452.2</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="4">
         <v>472</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="4">
         <v>429.7</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Refinery</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="n">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4">
         <v>0</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="4">
         <v>0</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="4">
         <v>0</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="4">
         <v>0</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="4">
         <v>0</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="4">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Iron &amp; Steel Manufacture</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="n">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4">
         <v>45.6</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="4">
         <v>42.7</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="4">
         <v>38.1</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>39.2</v>
-      </c>
-      <c r="F8" s="4" t="n">
+      <c r="E8" s="4">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="F8" s="4">
         <v>46.3</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="4">
         <v>45.6</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="4">
         <v>43.5</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Cement Manufacture</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="4">
         <v>11.7</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="4">
         <v>12.2</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="4">
         <v>10.9</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="4">
         <v>11.5</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="4">
         <v>11.7</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="4">
         <v>11.6</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="4">
         <v>10.1</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Ammonia Derivatives</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="n">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4">
         <v>21.9</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="4">
         <v>19.5</v>
       </c>
-      <c r="D10" s="4" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="E10" s="4" t="n">
+      <c r="D10" s="4">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E10" s="4">
         <v>16.2</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="4">
         <v>19.7</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="4">
         <v>19.5</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="4">
         <v>9.5</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Gas Processing</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="n">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="4">
         <v>21.4</v>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="D11" s="4" t="n">
+      <c r="C11" s="4">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="D11" s="4">
         <v>16.3</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="4">
         <v>18.3</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="4">
         <v>16.8</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="4">
         <v>16.7</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="4">
         <v>16.7</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Gas to Liquids</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="C12" s="4" t="n">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="C12" s="4">
         <v>3.3</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="4">
         <v>7.9</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="4">
         <v>0</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="4">
         <v>0</v>
       </c>
-      <c r="G12" s="4" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NGC 4" Sales to bpTT</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="4" t="inlineStr"/>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="n">
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4">
         <v>0.9</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="4">
         <v>1</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="4">
         <v>0.8</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Small Consumers</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="D14" s="4" t="n">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="4">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="C14" s="4">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D14" s="4">
         <v>9.9</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="4">
         <v>9.6</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="4">
         <v>9.1</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="4">
         <v>8.9</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="4">
         <v>9.5</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Liquefied Natural Gas (LNG)</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>1062.6</v>
-      </c>
-      <c r="C15" s="4" t="n">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1062.5999999999999</v>
+      </c>
+      <c r="C15" s="4">
         <v>1203.2</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="4">
         <v>1171.5</v>
       </c>
-      <c r="E15" s="4" t="n">
-        <v>1071.6</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>1137.1</v>
-      </c>
-      <c r="G15" s="4" t="n">
+      <c r="E15" s="4">
+        <v>1071.5999999999999</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1137.0999999999999</v>
+      </c>
+      <c r="G15" s="4">
         <v>1128.2</v>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>1157.6</v>
+      <c r="H15" s="4">
+        <v>1157.5999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="37" customWidth="1"/>
+    <col min="2" max="7" width="21" customWidth="1"/>
+    <col min="8" max="8" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3">
+        <v>2677.6</v>
+      </c>
+      <c r="C2" s="3">
+        <v>2598.6999999999998</v>
+      </c>
+      <c r="D2" s="3">
+        <v>2511.4</v>
+      </c>
+      <c r="E2" s="3">
+        <v>2592.1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>2442.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2576.1</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2506.9</v>
+      </c>
+      <c r="D3" s="3">
+        <v>2394.6999999999998</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2424</v>
+      </c>
+      <c r="F3" s="3">
+        <v>2273.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="4">
+        <v>266.8</v>
+      </c>
+      <c r="C4" s="4">
+        <v>258.10000000000002</v>
+      </c>
+      <c r="D4" s="4">
+        <v>266.5</v>
+      </c>
+      <c r="E4" s="4">
+        <v>268</v>
+      </c>
+      <c r="F4" s="4">
+        <v>250.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="4">
+        <v>483.5</v>
+      </c>
+      <c r="C5" s="4">
+        <v>443.7</v>
+      </c>
+      <c r="D5" s="4">
+        <v>422.9</v>
+      </c>
+      <c r="E5" s="4">
+        <v>462.3</v>
+      </c>
+      <c r="F5" s="4">
+        <v>345.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="4">
+        <v>516.6</v>
+      </c>
+      <c r="C6" s="4">
+        <v>534.4</v>
+      </c>
+      <c r="D6" s="4">
+        <v>538.79999999999995</v>
+      </c>
+      <c r="E6" s="4">
+        <v>452.2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>429.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4">
+        <v>42.7</v>
+      </c>
+      <c r="C8" s="4">
+        <v>38.1</v>
+      </c>
+      <c r="D8" s="4">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46.3</v>
+      </c>
+      <c r="F8" s="4">
+        <v>43.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="4">
+        <v>12.2</v>
+      </c>
+      <c r="C9" s="4">
+        <v>10.9</v>
+      </c>
+      <c r="D9" s="4">
+        <v>11.5</v>
+      </c>
+      <c r="E9" s="4">
+        <v>11.7</v>
+      </c>
+      <c r="F9" s="4">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="4">
+        <v>19.5</v>
+      </c>
+      <c r="C10" s="4">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D10" s="4">
+        <v>16.2</v>
+      </c>
+      <c r="E10" s="4">
+        <v>19.7</v>
+      </c>
+      <c r="F10" s="4">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="4">
+        <v>18.899999999999999</v>
+      </c>
+      <c r="C11" s="4">
+        <v>16.3</v>
+      </c>
+      <c r="D11" s="4">
+        <v>18.3</v>
+      </c>
+      <c r="E11" s="4">
+        <v>16.8</v>
+      </c>
+      <c r="F11" s="4">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="4">
+        <v>3.3</v>
+      </c>
+      <c r="C12" s="4">
+        <v>7.9</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4">
+        <v>0.9</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="4">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="C14" s="4">
+        <v>9.9</v>
+      </c>
+      <c r="D14" s="4">
+        <v>9.6</v>
+      </c>
+      <c r="E14" s="4">
+        <v>9.1</v>
+      </c>
+      <c r="F14" s="4">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="4">
+        <v>1203.2</v>
+      </c>
+      <c r="C15" s="4">
+        <v>1171.5</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1071.5999999999999</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1137.0999999999999</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1157.5999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/TT_Nat_Gas_Prod_Util_2026.xlsx
+++ b/TT_Nat_Gas_Prod_Util_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Python-Projects\TT-Economic-Markers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28DA206C-25A3-44D3-B697-20D8D82B1028}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE4D5C65-37D8-4527-B290-3C3DA8C92C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
